--- a/artfynd/A 38570-2024 artfynd.xlsx
+++ b/artfynd/A 38570-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>17079133</v>
+        <v>137490370</v>
       </c>
       <c r="B5" t="n">
-        <v>106229</v>
+        <v>58032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,34 +1057,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221725</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Piteå, Nb</t>
+          <t>Svartnäsmyran-Månsgrönnan, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>809574</v>
+        <v>810220</v>
       </c>
       <c r="R5" t="n">
-        <v>7255024</v>
+        <v>7255599</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2012-07-01</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2012-07-01</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>allmän på platsen, möjlig säker reproduktion</t>
+          <t>läte</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,24 +1136,24 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tomas Lindberg</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tomas Lindberg</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17079133</t>
+          <t>https://artportalen.se/Sighting/137490370</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>17079134</v>
+        <v>17079133</v>
       </c>
       <c r="B6" t="n">
         <v>106229</v>
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>809422</v>
+        <v>809574</v>
       </c>
       <c r="R6" t="n">
-        <v>7254888</v>
+        <v>7255024</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1253,6 +1253,113 @@
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17079133</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>17079134</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Piteå, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>809422</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7254888</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2012-07-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2012-07-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>allmän på platsen, möjlig säker reproduktion</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Lindberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Lindberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/17079134</t>
         </is>
@@ -1265,6 +1372,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38570-2024 artfynd.xlsx
+++ b/artfynd/A 38570-2024 artfynd.xlsx
@@ -1049,7 +1049,7 @@
         <v>137490370</v>
       </c>
       <c r="B5" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
